--- a/템플릿/LH50억~100억(소방)_템플릿.xlsx
+++ b/템플릿/LH50억~100억(소방)_템플릿.xlsx
@@ -2044,6 +2044,99 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="9" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2109,99 +2202,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2497,7 +2497,8 @@
     <col min="8" max="8" width="8.109375" style="1" customWidth="1"/>
     <col min="9" max="10" width="8.77734375" style="1" customWidth="1"/>
     <col min="11" max="13" width="8.109375" style="1" customWidth="1"/>
-    <col min="14" max="15" width="5.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.77734375" style="1" customWidth="1"/>
     <col min="16" max="21" width="7.88671875" style="1" customWidth="1"/>
     <col min="22" max="22" width="7.6640625" style="121" hidden="1" customWidth="1"/>
     <col min="23" max="27" width="8.33203125" style="1" customWidth="1"/>
@@ -2505,9 +2506,9 @@
     <col min="29" max="29" width="7.6640625" style="121" hidden="1" customWidth="1"/>
     <col min="30" max="31" width="7.6640625" style="121" customWidth="1"/>
     <col min="32" max="33" width="6.109375" style="1" customWidth="1"/>
-    <col min="34" max="34" width="7.6640625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="7.88671875" style="1" customWidth="1"/>
     <col min="35" max="37" width="4.5546875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="6.77734375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="7.44140625" style="1" customWidth="1"/>
     <col min="39" max="39" width="7.88671875" style="1" customWidth="1"/>
     <col min="40" max="40" width="8.77734375" style="1" customWidth="1"/>
     <col min="41" max="41" width="7.5546875" style="1" customWidth="1"/>
@@ -2524,15 +2525,15 @@
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="244"/>
-      <c r="E1" s="244"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="275"/>
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="245"/>
-      <c r="J1" s="246"/>
+      <c r="I1" s="276"/>
+      <c r="J1" s="277"/>
       <c r="K1" s="7" t="s">
         <v>5</v>
       </c>
@@ -2547,31 +2548,31 @@
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
-      <c r="W1" s="247" t="s">
+      <c r="W1" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="247"/>
-      <c r="Y1" s="248" t="s">
+      <c r="X1" s="278"/>
+      <c r="Y1" s="279" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="249"/>
-      <c r="AA1" s="250" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="251"/>
+      <c r="Z1" s="280"/>
+      <c r="AA1" s="281" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="282"/>
       <c r="AC1" s="10"/>
       <c r="AD1" s="10"/>
-      <c r="AE1" s="252" t="s">
+      <c r="AE1" s="283" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="253"/>
-      <c r="AG1" s="232">
+      <c r="AF1" s="284"/>
+      <c r="AG1" s="263">
         <f>D1</f>
         <v>0</v>
       </c>
-      <c r="AH1" s="232"/>
-      <c r="AI1" s="232"/>
-      <c r="AJ1" s="232"/>
+      <c r="AH1" s="263"/>
+      <c r="AI1" s="263"/>
+      <c r="AJ1" s="263"/>
       <c r="AK1" s="11" t="s">
         <v>8</v>
       </c>
@@ -2586,58 +2587,58 @@
       <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
       <c r="F2" s="15"/>
       <c r="G2" s="16"/>
       <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="234">
+      <c r="I2" s="265">
         <f>D2*3</f>
         <v>0</v>
       </c>
-      <c r="J2" s="235"/>
+      <c r="J2" s="266"/>
       <c r="K2" s="17" t="s">
         <v>67</v>
       </c>
       <c r="L2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="236" t="s">
+      <c r="M2" s="267" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="237"/>
-      <c r="O2" s="237"/>
-      <c r="P2" s="237"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
       <c r="Q2" s="19"/>
       <c r="R2" s="19"/>
       <c r="S2" s="19"/>
       <c r="T2" s="20"/>
       <c r="U2" s="21"/>
       <c r="V2" s="21"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="239">
+      <c r="W2" s="269"/>
+      <c r="X2" s="269"/>
+      <c r="Y2" s="270">
         <f>I1</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="241" t="e">
+      <c r="Z2" s="271"/>
+      <c r="AA2" s="272" t="e">
         <f>TRUNC(W2/Y2,4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2" s="242"/>
+      <c r="AB2" s="273"/>
       <c r="AC2" s="22"/>
-      <c r="AD2" s="243"/>
-      <c r="AE2" s="243"/>
-      <c r="AF2" s="243"/>
-      <c r="AG2" s="243"/>
-      <c r="AH2" s="243"/>
-      <c r="AI2" s="243"/>
-      <c r="AJ2" s="243"/>
-      <c r="AK2" s="243"/>
-      <c r="AL2" s="243"/>
+      <c r="AD2" s="274"/>
+      <c r="AE2" s="274"/>
+      <c r="AF2" s="274"/>
+      <c r="AG2" s="274"/>
+      <c r="AH2" s="274"/>
+      <c r="AI2" s="274"/>
+      <c r="AJ2" s="274"/>
+      <c r="AK2" s="274"/>
+      <c r="AL2" s="274"/>
       <c r="AM2" s="133"/>
       <c r="AN2" s="24" t="s">
         <v>13</v>
@@ -2650,112 +2651,112 @@
       <c r="AT2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="AU2" s="258">
+      <c r="AU2" s="249">
         <f>AG1</f>
         <v>0</v>
       </c>
-      <c r="AV2" s="259"/>
+      <c r="AV2" s="250"/>
       <c r="AY2" s="27"/>
     </row>
     <row r="3" spans="1:52" s="28" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="260" t="s">
+      <c r="A3" s="251" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="262" t="s">
+      <c r="B3" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="264" t="s">
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257"/>
+      <c r="I3" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="265"/>
-      <c r="K3" s="265"/>
-      <c r="L3" s="265"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="267" t="s">
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="M3" s="257"/>
+      <c r="N3" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="269" t="s">
+      <c r="O3" s="260" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="264" t="s">
+      <c r="P3" s="255" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="265"/>
-      <c r="R3" s="271"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="266"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="257"/>
       <c r="V3" s="132"/>
-      <c r="W3" s="264" t="s">
+      <c r="W3" s="255" t="s">
         <v>22</v>
       </c>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
-      <c r="AA3" s="265"/>
-      <c r="AB3" s="265"/>
-      <c r="AC3" s="265"/>
-      <c r="AD3" s="265"/>
-      <c r="AE3" s="266"/>
-      <c r="AF3" s="264"/>
-      <c r="AG3" s="265"/>
-      <c r="AH3" s="265"/>
-      <c r="AI3" s="265"/>
-      <c r="AJ3" s="265"/>
-      <c r="AK3" s="265"/>
-      <c r="AL3" s="265"/>
-      <c r="AM3" s="266"/>
-      <c r="AN3" s="279" t="s">
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
+      <c r="AA3" s="256"/>
+      <c r="AB3" s="256"/>
+      <c r="AC3" s="256"/>
+      <c r="AD3" s="256"/>
+      <c r="AE3" s="257"/>
+      <c r="AF3" s="255"/>
+      <c r="AG3" s="256"/>
+      <c r="AH3" s="256"/>
+      <c r="AI3" s="256"/>
+      <c r="AJ3" s="256"/>
+      <c r="AK3" s="256"/>
+      <c r="AL3" s="256"/>
+      <c r="AM3" s="257"/>
+      <c r="AN3" s="242" t="s">
         <v>23</v>
       </c>
-      <c r="AO3" s="275" t="s">
+      <c r="AO3" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="AP3" s="281" t="s">
+      <c r="AP3" s="244" t="s">
         <v>25</v>
       </c>
-      <c r="AQ3" s="254" t="s">
+      <c r="AQ3" s="246" t="s">
         <v>26</v>
       </c>
-      <c r="AR3" s="256" t="s">
+      <c r="AR3" s="248" t="s">
         <v>27</v>
       </c>
-      <c r="AS3" s="257" t="s">
+      <c r="AS3" s="237" t="s">
         <v>28</v>
       </c>
-      <c r="AT3" s="275" t="s">
+      <c r="AT3" s="238" t="s">
         <v>29</v>
       </c>
-      <c r="AU3" s="257" t="s">
+      <c r="AU3" s="237" t="s">
         <v>30</v>
       </c>
-      <c r="AV3" s="257" t="s">
+      <c r="AV3" s="237" t="s">
         <v>31</v>
       </c>
-      <c r="AW3" s="257" t="s">
+      <c r="AW3" s="237" t="s">
         <v>32</v>
       </c>
-      <c r="AX3" s="277" t="s">
+      <c r="AX3" s="240" t="s">
         <v>33</v>
       </c>
-      <c r="AY3" s="257" t="s">
+      <c r="AY3" s="237" t="s">
         <v>34</v>
       </c>
-      <c r="AZ3" s="257" t="s">
+      <c r="AZ3" s="237" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:52" s="28" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="261"/>
-      <c r="B4" s="263"/>
+      <c r="A4" s="252"/>
+      <c r="B4" s="254"/>
       <c r="C4" s="29" t="s">
         <v>36</v>
       </c>
@@ -2789,8 +2790,8 @@
       <c r="M4" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="268"/>
-      <c r="O4" s="270"/>
+      <c r="N4" s="259"/>
+      <c r="O4" s="261"/>
       <c r="P4" s="33" t="s">
         <v>44</v>
       </c>
@@ -2861,19 +2862,19 @@
       <c r="AM4" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="AN4" s="280"/>
-      <c r="AO4" s="276"/>
-      <c r="AP4" s="282"/>
-      <c r="AQ4" s="255"/>
-      <c r="AR4" s="256"/>
-      <c r="AS4" s="257"/>
-      <c r="AT4" s="276"/>
-      <c r="AU4" s="257"/>
-      <c r="AV4" s="257"/>
-      <c r="AW4" s="257"/>
-      <c r="AX4" s="278"/>
-      <c r="AY4" s="257"/>
-      <c r="AZ4" s="257"/>
+      <c r="AN4" s="243"/>
+      <c r="AO4" s="239"/>
+      <c r="AP4" s="245"/>
+      <c r="AQ4" s="247"/>
+      <c r="AR4" s="248"/>
+      <c r="AS4" s="237"/>
+      <c r="AT4" s="239"/>
+      <c r="AU4" s="237"/>
+      <c r="AV4" s="237"/>
+      <c r="AW4" s="237"/>
+      <c r="AX4" s="241"/>
+      <c r="AY4" s="237"/>
+      <c r="AZ4" s="237"/>
     </row>
     <row r="5" spans="1:52" s="75" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45"/>
@@ -2982,13 +2983,13 @@
     <row r="6" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45"/>
       <c r="B6" s="46"/>
-      <c r="C6" s="272" t="s">
+      <c r="C6" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="273"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="273"/>
-      <c r="G6" s="274"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="234"/>
       <c r="H6" s="122"/>
       <c r="I6" s="89"/>
       <c r="J6" s="130"/>
@@ -3144,13 +3145,13 @@
     <row r="8" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45"/>
       <c r="B8" s="46"/>
-      <c r="C8" s="272" t="s">
+      <c r="C8" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="273"/>
-      <c r="E8" s="273"/>
-      <c r="F8" s="273"/>
-      <c r="G8" s="274"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="234"/>
       <c r="H8" s="122"/>
       <c r="I8" s="89"/>
       <c r="J8" s="130"/>
@@ -3257,7 +3258,7 @@
       <c r="AF9" s="165"/>
       <c r="AG9" s="62"/>
       <c r="AH9" s="66" t="e">
-        <f t="shared" si="6"/>
+        <f>IF((V9+AE9+AF9)&gt;=30,30,(V9+AE9+AF9))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AI9" s="64">
@@ -3308,13 +3309,13 @@
     <row r="10" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="272" t="s">
+      <c r="C10" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="273"/>
-      <c r="E10" s="273"/>
-      <c r="F10" s="273"/>
-      <c r="G10" s="274"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="234"/>
       <c r="H10" s="122"/>
       <c r="I10" s="89"/>
       <c r="J10" s="130"/>
@@ -3472,13 +3473,13 @@
     <row r="12" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="272" t="s">
+      <c r="C12" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="273"/>
-      <c r="E12" s="273"/>
-      <c r="F12" s="273"/>
-      <c r="G12" s="274"/>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="234"/>
       <c r="H12" s="122"/>
       <c r="I12" s="130"/>
       <c r="J12" s="130"/>
@@ -3633,13 +3634,13 @@
     <row r="14" spans="1:52" s="75" customFormat="1" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="272" t="s">
+      <c r="C14" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="273"/>
-      <c r="E14" s="273"/>
-      <c r="F14" s="273"/>
-      <c r="G14" s="274"/>
+      <c r="D14" s="233"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="234"/>
       <c r="H14" s="122"/>
       <c r="I14" s="89"/>
       <c r="J14" s="130"/>
@@ -3798,13 +3799,13 @@
     <row r="16" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="272" t="s">
+      <c r="C16" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="273"/>
-      <c r="E16" s="273"/>
-      <c r="F16" s="273"/>
-      <c r="G16" s="283"/>
+      <c r="D16" s="233"/>
+      <c r="E16" s="233"/>
+      <c r="F16" s="233"/>
+      <c r="G16" s="235"/>
       <c r="H16" s="122"/>
       <c r="I16" s="89"/>
       <c r="J16" s="89"/>
@@ -3962,13 +3963,13 @@
     <row r="18" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="272" t="s">
+      <c r="C18" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="273"/>
-      <c r="E18" s="273"/>
-      <c r="F18" s="273"/>
-      <c r="G18" s="283"/>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="235"/>
       <c r="H18" s="122"/>
       <c r="I18" s="89"/>
       <c r="J18" s="89"/>
@@ -4125,13 +4126,13 @@
     <row r="20" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="272" t="s">
+      <c r="C20" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="273"/>
-      <c r="E20" s="273"/>
-      <c r="F20" s="273"/>
-      <c r="G20" s="283"/>
+      <c r="D20" s="233"/>
+      <c r="E20" s="233"/>
+      <c r="F20" s="233"/>
+      <c r="G20" s="235"/>
       <c r="H20" s="122"/>
       <c r="I20" s="89"/>
       <c r="J20" s="89"/>
@@ -4288,13 +4289,13 @@
     <row r="22" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="272" t="s">
+      <c r="C22" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="273"/>
-      <c r="E22" s="273"/>
-      <c r="F22" s="273"/>
-      <c r="G22" s="284"/>
+      <c r="D22" s="233"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="236"/>
       <c r="H22" s="122"/>
       <c r="I22" s="130"/>
       <c r="J22" s="130"/>
@@ -4451,13 +4452,13 @@
     <row r="24" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="272" t="s">
+      <c r="C24" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="273"/>
-      <c r="E24" s="273"/>
-      <c r="F24" s="273"/>
-      <c r="G24" s="274"/>
+      <c r="D24" s="233"/>
+      <c r="E24" s="233"/>
+      <c r="F24" s="233"/>
+      <c r="G24" s="234"/>
       <c r="H24" s="122"/>
       <c r="I24" s="130"/>
       <c r="J24" s="89"/>
@@ -4614,13 +4615,13 @@
     <row r="26" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="272" t="s">
+      <c r="C26" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="273"/>
-      <c r="E26" s="273"/>
-      <c r="F26" s="273"/>
-      <c r="G26" s="274"/>
+      <c r="D26" s="233"/>
+      <c r="E26" s="233"/>
+      <c r="F26" s="233"/>
+      <c r="G26" s="234"/>
       <c r="H26" s="122"/>
       <c r="I26" s="89"/>
       <c r="J26" s="89"/>
@@ -4777,13 +4778,13 @@
     <row r="28" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="272" t="s">
+      <c r="C28" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="273"/>
-      <c r="E28" s="273"/>
-      <c r="F28" s="273"/>
-      <c r="G28" s="274"/>
+      <c r="D28" s="233"/>
+      <c r="E28" s="233"/>
+      <c r="F28" s="233"/>
+      <c r="G28" s="234"/>
       <c r="H28" s="122"/>
       <c r="I28" s="130"/>
       <c r="J28" s="89"/>
@@ -4942,13 +4943,13 @@
     <row r="30" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="272" t="s">
+      <c r="C30" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="273"/>
-      <c r="E30" s="273"/>
-      <c r="F30" s="273"/>
-      <c r="G30" s="274"/>
+      <c r="D30" s="233"/>
+      <c r="E30" s="233"/>
+      <c r="F30" s="233"/>
+      <c r="G30" s="234"/>
       <c r="H30" s="122"/>
       <c r="I30" s="130"/>
       <c r="J30" s="89"/>
@@ -5105,13 +5106,13 @@
     <row r="32" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="272" t="s">
+      <c r="C32" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="273"/>
-      <c r="E32" s="273"/>
-      <c r="F32" s="273"/>
-      <c r="G32" s="274"/>
+      <c r="D32" s="233"/>
+      <c r="E32" s="233"/>
+      <c r="F32" s="233"/>
+      <c r="G32" s="234"/>
       <c r="H32" s="122"/>
       <c r="I32" s="130"/>
       <c r="J32" s="130"/>
@@ -5268,13 +5269,13 @@
     <row r="34" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="272" t="s">
+      <c r="C34" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="273"/>
-      <c r="E34" s="273"/>
-      <c r="F34" s="273"/>
-      <c r="G34" s="274"/>
+      <c r="D34" s="233"/>
+      <c r="E34" s="233"/>
+      <c r="F34" s="233"/>
+      <c r="G34" s="234"/>
       <c r="H34" s="122"/>
       <c r="I34" s="130"/>
       <c r="J34" s="130"/>
@@ -5431,13 +5432,13 @@
     <row r="36" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="272" t="s">
+      <c r="C36" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="273"/>
-      <c r="E36" s="273"/>
-      <c r="F36" s="273"/>
-      <c r="G36" s="274"/>
+      <c r="D36" s="233"/>
+      <c r="E36" s="233"/>
+      <c r="F36" s="233"/>
+      <c r="G36" s="234"/>
       <c r="H36" s="122"/>
       <c r="I36" s="130"/>
       <c r="J36" s="89"/>
@@ -5596,13 +5597,13 @@
     <row r="38" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="272" t="s">
+      <c r="C38" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="273"/>
-      <c r="E38" s="273"/>
-      <c r="F38" s="273"/>
-      <c r="G38" s="274"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="234"/>
       <c r="H38" s="122"/>
       <c r="I38" s="130"/>
       <c r="J38" s="89"/>
@@ -5759,13 +5760,13 @@
     <row r="40" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="45"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="272" t="s">
+      <c r="C40" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="273"/>
-      <c r="E40" s="273"/>
-      <c r="F40" s="273"/>
-      <c r="G40" s="274"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="234"/>
       <c r="H40" s="122"/>
       <c r="I40" s="130"/>
       <c r="J40" s="130"/>
@@ -5926,13 +5927,13 @@
     <row r="42" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="272" t="s">
+      <c r="C42" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="273"/>
-      <c r="E42" s="273"/>
-      <c r="F42" s="273"/>
-      <c r="G42" s="274"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="234"/>
       <c r="H42" s="122"/>
       <c r="I42" s="89"/>
       <c r="J42" s="130"/>
@@ -6093,13 +6094,13 @@
     <row r="44" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="272" t="s">
+      <c r="C44" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="273"/>
-      <c r="E44" s="273"/>
-      <c r="F44" s="273"/>
-      <c r="G44" s="274"/>
+      <c r="D44" s="233"/>
+      <c r="E44" s="233"/>
+      <c r="F44" s="233"/>
+      <c r="G44" s="234"/>
       <c r="H44" s="122"/>
       <c r="I44" s="130"/>
       <c r="J44" s="130"/>
@@ -6257,13 +6258,13 @@
     <row r="46" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="45"/>
       <c r="B46" s="87"/>
-      <c r="C46" s="272" t="s">
+      <c r="C46" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="273"/>
-      <c r="E46" s="273"/>
-      <c r="F46" s="273"/>
-      <c r="G46" s="274"/>
+      <c r="D46" s="233"/>
+      <c r="E46" s="233"/>
+      <c r="F46" s="233"/>
+      <c r="G46" s="234"/>
       <c r="H46" s="122"/>
       <c r="I46" s="89"/>
       <c r="J46" s="130"/>
@@ -6421,13 +6422,13 @@
     <row r="48" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="272" t="s">
+      <c r="C48" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="273"/>
-      <c r="E48" s="273"/>
-      <c r="F48" s="273"/>
-      <c r="G48" s="274"/>
+      <c r="D48" s="233"/>
+      <c r="E48" s="233"/>
+      <c r="F48" s="233"/>
+      <c r="G48" s="234"/>
       <c r="H48" s="122"/>
       <c r="I48" s="89"/>
       <c r="J48" s="130"/>
@@ -6584,13 +6585,13 @@
     <row r="50" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="45"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="272" t="s">
+      <c r="C50" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="273"/>
-      <c r="E50" s="273"/>
-      <c r="F50" s="273"/>
-      <c r="G50" s="274"/>
+      <c r="D50" s="233"/>
+      <c r="E50" s="233"/>
+      <c r="F50" s="233"/>
+      <c r="G50" s="234"/>
       <c r="H50" s="122"/>
       <c r="I50" s="89"/>
       <c r="J50" s="130"/>
@@ -6746,13 +6747,13 @@
     <row r="52" spans="1:52" s="75" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A52" s="45"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="272" t="s">
+      <c r="C52" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="273"/>
-      <c r="E52" s="273"/>
-      <c r="F52" s="273"/>
-      <c r="G52" s="274"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="234"/>
       <c r="H52" s="122"/>
       <c r="I52" s="89"/>
       <c r="J52" s="130"/>
@@ -6909,13 +6910,13 @@
     <row r="54" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="45"/>
       <c r="B54" s="46"/>
-      <c r="C54" s="272" t="s">
+      <c r="C54" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D54" s="273"/>
-      <c r="E54" s="273"/>
-      <c r="F54" s="273"/>
-      <c r="G54" s="274"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="233"/>
+      <c r="F54" s="233"/>
+      <c r="G54" s="234"/>
       <c r="H54" s="122"/>
       <c r="I54" s="220"/>
       <c r="J54" s="89"/>
@@ -7072,13 +7073,13 @@
     <row r="56" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="45"/>
       <c r="B56" s="46"/>
-      <c r="C56" s="272" t="s">
+      <c r="C56" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D56" s="273"/>
-      <c r="E56" s="273"/>
-      <c r="F56" s="273"/>
-      <c r="G56" s="274"/>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="234"/>
       <c r="H56" s="122"/>
       <c r="I56" s="220"/>
       <c r="J56" s="89"/>
@@ -7233,13 +7234,13 @@
     <row r="58" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
       <c r="B58" s="46"/>
-      <c r="C58" s="272" t="s">
+      <c r="C58" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D58" s="273"/>
-      <c r="E58" s="273"/>
-      <c r="F58" s="273"/>
-      <c r="G58" s="274"/>
+      <c r="D58" s="233"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="233"/>
+      <c r="G58" s="234"/>
       <c r="H58" s="122"/>
       <c r="I58" s="220"/>
       <c r="J58" s="89"/>
@@ -7395,13 +7396,13 @@
     <row r="60" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A60" s="45"/>
       <c r="B60" s="46"/>
-      <c r="C60" s="272" t="s">
+      <c r="C60" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D60" s="273"/>
-      <c r="E60" s="273"/>
-      <c r="F60" s="273"/>
-      <c r="G60" s="274"/>
+      <c r="D60" s="233"/>
+      <c r="E60" s="233"/>
+      <c r="F60" s="233"/>
+      <c r="G60" s="234"/>
       <c r="H60" s="122"/>
       <c r="I60" s="220"/>
       <c r="J60" s="89"/>
@@ -7559,13 +7560,13 @@
     <row r="62" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A62" s="45"/>
       <c r="B62" s="46"/>
-      <c r="C62" s="272" t="s">
+      <c r="C62" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D62" s="273"/>
-      <c r="E62" s="273"/>
-      <c r="F62" s="273"/>
-      <c r="G62" s="274"/>
+      <c r="D62" s="233"/>
+      <c r="E62" s="233"/>
+      <c r="F62" s="233"/>
+      <c r="G62" s="234"/>
       <c r="H62" s="122"/>
       <c r="I62" s="220"/>
       <c r="J62" s="89"/>
@@ -7724,13 +7725,13 @@
     <row r="64" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A64" s="45"/>
       <c r="B64" s="46"/>
-      <c r="C64" s="272" t="s">
+      <c r="C64" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="273"/>
-      <c r="E64" s="273"/>
-      <c r="F64" s="273"/>
-      <c r="G64" s="274"/>
+      <c r="D64" s="233"/>
+      <c r="E64" s="233"/>
+      <c r="F64" s="233"/>
+      <c r="G64" s="234"/>
       <c r="H64" s="122"/>
       <c r="I64" s="220"/>
       <c r="J64" s="89"/>
@@ -7889,13 +7890,13 @@
     <row r="66" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A66" s="45"/>
       <c r="B66" s="46"/>
-      <c r="C66" s="272" t="s">
+      <c r="C66" s="232" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="273"/>
-      <c r="E66" s="273"/>
-      <c r="F66" s="273"/>
-      <c r="G66" s="274"/>
+      <c r="D66" s="233"/>
+      <c r="E66" s="233"/>
+      <c r="F66" s="233"/>
+      <c r="G66" s="234"/>
       <c r="H66" s="122"/>
       <c r="I66" s="220"/>
       <c r="J66" s="89"/>
@@ -8054,13 +8055,13 @@
     <row r="68" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A68" s="45"/>
       <c r="B68" s="46"/>
-      <c r="C68" s="272" t="s">
+      <c r="C68" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D68" s="273"/>
-      <c r="E68" s="273"/>
-      <c r="F68" s="273"/>
-      <c r="G68" s="274"/>
+      <c r="D68" s="233"/>
+      <c r="E68" s="233"/>
+      <c r="F68" s="233"/>
+      <c r="G68" s="234"/>
       <c r="H68" s="122"/>
       <c r="I68" s="220"/>
       <c r="J68" s="89"/>
@@ -8219,13 +8220,13 @@
     <row r="70" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A70" s="45"/>
       <c r="B70" s="46"/>
-      <c r="C70" s="272" t="s">
+      <c r="C70" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D70" s="273"/>
-      <c r="E70" s="273"/>
-      <c r="F70" s="273"/>
-      <c r="G70" s="274"/>
+      <c r="D70" s="233"/>
+      <c r="E70" s="233"/>
+      <c r="F70" s="233"/>
+      <c r="G70" s="234"/>
       <c r="H70" s="122"/>
       <c r="I70" s="220"/>
       <c r="J70" s="89"/>
@@ -8384,13 +8385,13 @@
     <row r="72" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A72" s="45"/>
       <c r="B72" s="46"/>
-      <c r="C72" s="272" t="s">
+      <c r="C72" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D72" s="273"/>
-      <c r="E72" s="273"/>
-      <c r="F72" s="273"/>
-      <c r="G72" s="274"/>
+      <c r="D72" s="233"/>
+      <c r="E72" s="233"/>
+      <c r="F72" s="233"/>
+      <c r="G72" s="234"/>
       <c r="H72" s="122"/>
       <c r="I72" s="220"/>
       <c r="J72" s="89"/>
@@ -8549,13 +8550,13 @@
     <row r="74" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A74" s="45"/>
       <c r="B74" s="46"/>
-      <c r="C74" s="272" t="s">
+      <c r="C74" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D74" s="273"/>
-      <c r="E74" s="273"/>
-      <c r="F74" s="273"/>
-      <c r="G74" s="274"/>
+      <c r="D74" s="233"/>
+      <c r="E74" s="233"/>
+      <c r="F74" s="233"/>
+      <c r="G74" s="234"/>
       <c r="H74" s="122"/>
       <c r="I74" s="220"/>
       <c r="J74" s="89"/>
@@ -8714,13 +8715,13 @@
     <row r="76" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A76" s="45"/>
       <c r="B76" s="46"/>
-      <c r="C76" s="272" t="s">
+      <c r="C76" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D76" s="273"/>
-      <c r="E76" s="273"/>
-      <c r="F76" s="273"/>
-      <c r="G76" s="274"/>
+      <c r="D76" s="233"/>
+      <c r="E76" s="233"/>
+      <c r="F76" s="233"/>
+      <c r="G76" s="234"/>
       <c r="H76" s="122"/>
       <c r="I76" s="220"/>
       <c r="J76" s="89"/>
@@ -8879,13 +8880,13 @@
     <row r="78" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A78" s="45"/>
       <c r="B78" s="46"/>
-      <c r="C78" s="272" t="s">
+      <c r="C78" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="273"/>
-      <c r="E78" s="273"/>
-      <c r="F78" s="273"/>
-      <c r="G78" s="274"/>
+      <c r="D78" s="233"/>
+      <c r="E78" s="233"/>
+      <c r="F78" s="233"/>
+      <c r="G78" s="234"/>
       <c r="H78" s="122"/>
       <c r="I78" s="220"/>
       <c r="J78" s="89"/>
@@ -9044,13 +9045,13 @@
     <row r="80" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A80" s="45"/>
       <c r="B80" s="46"/>
-      <c r="C80" s="272" t="s">
+      <c r="C80" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D80" s="273"/>
-      <c r="E80" s="273"/>
-      <c r="F80" s="273"/>
-      <c r="G80" s="274"/>
+      <c r="D80" s="233"/>
+      <c r="E80" s="233"/>
+      <c r="F80" s="233"/>
+      <c r="G80" s="234"/>
       <c r="H80" s="122"/>
       <c r="I80" s="220"/>
       <c r="J80" s="89"/>
@@ -9209,13 +9210,13 @@
     <row r="82" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A82" s="45"/>
       <c r="B82" s="46"/>
-      <c r="C82" s="272" t="s">
+      <c r="C82" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="D82" s="273"/>
-      <c r="E82" s="273"/>
-      <c r="F82" s="273"/>
-      <c r="G82" s="274"/>
+      <c r="D82" s="233"/>
+      <c r="E82" s="233"/>
+      <c r="F82" s="233"/>
+      <c r="G82" s="234"/>
       <c r="H82" s="122"/>
       <c r="I82" s="220"/>
       <c r="J82" s="89"/>
@@ -9374,13 +9375,13 @@
     <row r="84" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A84" s="45"/>
       <c r="B84" s="46"/>
-      <c r="C84" s="272" t="s">
+      <c r="C84" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="D84" s="273"/>
-      <c r="E84" s="273"/>
-      <c r="F84" s="273"/>
-      <c r="G84" s="274"/>
+      <c r="D84" s="233"/>
+      <c r="E84" s="233"/>
+      <c r="F84" s="233"/>
+      <c r="G84" s="234"/>
       <c r="H84" s="122"/>
       <c r="I84" s="220"/>
       <c r="J84" s="89"/>
@@ -9539,13 +9540,13 @@
     <row r="86" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A86" s="45"/>
       <c r="B86" s="46"/>
-      <c r="C86" s="272" t="s">
+      <c r="C86" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D86" s="273"/>
-      <c r="E86" s="273"/>
-      <c r="F86" s="273"/>
-      <c r="G86" s="274"/>
+      <c r="D86" s="233"/>
+      <c r="E86" s="233"/>
+      <c r="F86" s="233"/>
+      <c r="G86" s="234"/>
       <c r="H86" s="122"/>
       <c r="I86" s="220"/>
       <c r="J86" s="89"/>
@@ -9704,13 +9705,13 @@
     <row r="88" spans="1:52" s="75" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A88" s="45"/>
       <c r="B88" s="46"/>
-      <c r="C88" s="272" t="s">
+      <c r="C88" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="D88" s="273"/>
-      <c r="E88" s="273"/>
-      <c r="F88" s="273"/>
-      <c r="G88" s="274"/>
+      <c r="D88" s="233"/>
+      <c r="E88" s="233"/>
+      <c r="F88" s="233"/>
+      <c r="G88" s="234"/>
       <c r="H88" s="122"/>
       <c r="I88" s="220"/>
       <c r="J88" s="89"/>
@@ -15692,42 +15693,33 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AD2:AL2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="AF3:AM3"/>
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="AZ3:AZ4"/>
     <mergeCell ref="C6:G6"/>
@@ -15744,33 +15736,42 @@
     <mergeCell ref="AN3:AN4"/>
     <mergeCell ref="AO3:AO4"/>
     <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="AF3:AM3"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AD2:AL2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C86:G86"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
